--- a/src/main/python/av_energy/scenarios/robotaxi_2025_baseline.xlsx
+++ b/src/main/python/av_energy/scenarios/robotaxi_2025_baseline.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haitamlaarabi/Workspace/Models/beam/freight-develop/src/main/python/av_energy/scenarios/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EA145113-6255-5841-822E-A9FCB33E372B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83958D25-AF55-DD4F-B080-F688A24A854A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="820" windowWidth="28040" windowHeight="17440" xr2:uid="{AA04B16E-9AEE-2A45-AF09-5118A5DC29DB}"/>
+    <workbookView xWindow="25960" yWindow="500" windowWidth="40920" windowHeight="24900" xr2:uid="{AA04B16E-9AEE-2A45-AF09-5118A5DC29DB}"/>
   </bookViews>
   <sheets>
     <sheet name="robotaxi_2025_baseline" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="132">
   <si>
     <t>Company</t>
   </si>
@@ -400,6 +400,39 @@
   </si>
   <si>
     <t>Miles simulated by Avs Annually in 2030</t>
+  </si>
+  <si>
+    <t>https://www.fhwa.dot.gov/policyinformation/statistics/2023/vm1.cfm</t>
+  </si>
+  <si>
+    <t>Projected Fleet 2025</t>
+  </si>
+  <si>
+    <t>Number of motor vehicles registered 2022</t>
+  </si>
+  <si>
+    <t>Number of motor vehicles registered 2023</t>
+  </si>
+  <si>
+    <t>Average miles traveled per vehicle 2022</t>
+  </si>
+  <si>
+    <t>Average miles traveled per vehicle 2023</t>
+  </si>
+  <si>
+    <t>Total miles traveled 2022</t>
+  </si>
+  <si>
+    <t>Total miles traveled 2023</t>
+  </si>
+  <si>
+    <t>Total miles traveled 2025</t>
+  </si>
+  <si>
+    <t>Total Vehicles (+ AV) 2025</t>
+  </si>
+  <si>
+    <t>Total miles traveled (+AV) 2025</t>
   </si>
 </sst>
 </file>
@@ -904,7 +937,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="43"/>
@@ -917,6 +950,7 @@
     <xf numFmtId="1" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Accent1" xfId="20" builtinId="30" customBuiltin="1"/>
@@ -1294,11 +1328,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94EC164D-2282-194A-9A88-8ACA14A35BFA}">
-  <dimension ref="A1:P38"/>
+  <dimension ref="A1:P52"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="34.5" customWidth="1"/>
-    <col min="2" max="2" width="24.5" customWidth="1"/>
+    <col min="1" max="1" width="37" customWidth="1"/>
+    <col min="2" max="2" width="25.5" customWidth="1"/>
     <col min="3" max="3" width="47" customWidth="1"/>
     <col min="4" max="6" width="25" customWidth="1"/>
     <col min="7" max="7" width="27.83203125" customWidth="1"/>
@@ -1385,7 +1419,7 @@
         <v>109</v>
       </c>
       <c r="H2">
-        <f>D2/B2</f>
+        <f t="shared" ref="H2:H13" si="0">D2/B2</f>
         <v>22000</v>
       </c>
       <c r="I2">
@@ -1421,7 +1455,7 @@
         <v>13</v>
       </c>
       <c r="H3">
-        <f>D3/B3</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I3">
@@ -1451,7 +1485,7 @@
         <v>19</v>
       </c>
       <c r="H4">
-        <f>D4/B4</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I4">
@@ -1484,7 +1518,7 @@
         <v>25</v>
       </c>
       <c r="H5">
-        <f>D5/B5</f>
+        <f t="shared" si="0"/>
         <v>93787.5</v>
       </c>
       <c r="I5">
@@ -1517,7 +1551,7 @@
         <v>31</v>
       </c>
       <c r="H6">
-        <f>D6/B6</f>
+        <f t="shared" si="0"/>
         <v>24038.461538461539</v>
       </c>
       <c r="I6">
@@ -1547,7 +1581,7 @@
         <v>36</v>
       </c>
       <c r="H7">
-        <f>D7/B7</f>
+        <f t="shared" si="0"/>
         <v>10000</v>
       </c>
       <c r="I7">
@@ -1580,7 +1614,7 @@
         <v>42</v>
       </c>
       <c r="H8">
-        <f>D8/B8</f>
+        <f t="shared" si="0"/>
         <v>12500</v>
       </c>
       <c r="I8">
@@ -1616,7 +1650,7 @@
         <v>48</v>
       </c>
       <c r="H9">
-        <f>D9/B9</f>
+        <f t="shared" si="0"/>
         <v>28000</v>
       </c>
       <c r="I9">
@@ -1646,7 +1680,7 @@
         <v>53</v>
       </c>
       <c r="H10">
-        <f>D10/B10</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I10">
@@ -1670,7 +1704,7 @@
         <v>56</v>
       </c>
       <c r="H11">
-        <f>D11/B11</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I11">
@@ -1700,7 +1734,7 @@
         <v>62</v>
       </c>
       <c r="H12">
-        <f>D12/B12</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I12">
@@ -1727,7 +1761,7 @@
         <v>92</v>
       </c>
       <c r="H13">
-        <f>D13/B13</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I13">
@@ -1975,7 +2009,7 @@
         <v>577332.75600000005</v>
       </c>
     </row>
-    <row r="33" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A33" s="6" t="s">
         <v>116</v>
       </c>
@@ -1984,7 +2018,7 @@
         <v>40413333.333333336</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>117</v>
       </c>
@@ -1993,7 +2027,7 @@
         <v>205530461.13600001</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>118</v>
       </c>
@@ -2002,7 +2036,7 @@
         <v>14387146666.666668</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>119</v>
       </c>
@@ -2011,7 +2045,7 @@
         <v>11082672028.427999</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>120</v>
       </c>
@@ -2020,13 +2054,108 @@
         <v>212746666481713.34</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B38" s="5"/>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>123</v>
+      </c>
+      <c r="B41">
+        <v>282174766</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>124</v>
+      </c>
+      <c r="B42">
+        <v>284614269</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>122</v>
+      </c>
+      <c r="B43">
+        <f>B42+((B42-B41)*(2025-2023))</f>
+        <v>289493275</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>130</v>
+      </c>
+      <c r="B44">
+        <f>B43+B19</f>
+        <v>289496306</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>125</v>
+      </c>
+      <c r="B46">
+        <v>11327</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>126</v>
+      </c>
+      <c r="B47">
+        <v>11408</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>127</v>
+      </c>
+      <c r="B49">
+        <f>B46*B41</f>
+        <v>3196193574482</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>128</v>
+      </c>
+      <c r="B50">
+        <f>B47*B42</f>
+        <v>3246879580752</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>129</v>
+      </c>
+      <c r="B51">
+        <f>B50+((B50-B49)*(2025-2023))</f>
+        <v>3348251593292</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>131</v>
+      </c>
+      <c r="B52" s="10">
+        <f>B51+B34</f>
+        <v>3348457123753.1362</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="P2" r:id="rId1" xr:uid="{9A3C5286-02CD-044F-9342-E892935C8E17}"/>
+    <hyperlink ref="C41" r:id="rId2" xr:uid="{1D32FEC7-118E-3740-93EF-25D4DED08C51}"/>
+    <hyperlink ref="C42" r:id="rId3" xr:uid="{9E10B614-D13B-3F44-A847-ED603C07BB00}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>